--- a/partner_results/unknown_complete/ClassMissingEnglishDefinition_unknown.xlsx
+++ b/partner_results/unknown_complete/ClassMissingEnglishDefinition_unknown.xlsx
@@ -446,37 +446,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>nitrogen molecular entity</t>
+          <t>lanthanoid atom</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>pnictogen molecular entity</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>aluminium oxide</t>
+          <t>lanthanum atom</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>molecular entity</t>
+          <t>lanthanoid atom</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>rubidium atom</t>
+          <t>barium atom</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -485,13 +493,17 @@
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>gold atom</t>
+          <t>platinum</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -500,28 +512,36 @@
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>californium atom</t>
+          <t>fluoride</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>molecular entity</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>curium atom</t>
+          <t>magnesium atom</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -530,13 +550,17 @@
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>americium atom</t>
+          <t>caesium atom</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -545,13 +569,17 @@
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>tin atom</t>
+          <t>actinium atom</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -560,58 +588,74 @@
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>fluoride</t>
+          <t>scandium atom</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>molecular entity</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>organosulfur heterocyclic compound</t>
+          <t>helium atom</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>organic heterocyclic compound</t>
+          <t>molecular entity</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>nitrogen atom</t>
+          <t>Homo sapiens</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nonmetal atom</t>
+          <t>material entity</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>lutetium atom</t>
+          <t>thulium atom</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -620,13 +664,17 @@
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>rhenium atom</t>
+          <t>calcium atom</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -635,13 +683,17 @@
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>carbon atom</t>
+          <t>bromine atom</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -650,43 +702,55 @@
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>darmstadtium</t>
+          <t>tetraphosphorus decaoxide</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>molecular entity</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>carbon group molecular entity</t>
+          <t>nonmetal atom</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>p-block molecular entity</t>
+          <t>atom</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>fluorine atom</t>
+          <t>hydrogen atom</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -695,13 +759,17 @@
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>lithium atom</t>
+          <t>gold atom</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -710,88 +778,112 @@
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>thorium</t>
+          <t>europium atom</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>lanthanoid atom</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>platinum</t>
+          <t>sulfur molecular entity</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>chalcogen molecular entity</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>praseodymium atom</t>
+          <t>bohrium atom</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>lanthanoid atom</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>niobium atom</t>
+          <t>neodymium atom</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>lanthanoid atom</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>tellurium atom</t>
+          <t>lawrencium atom</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>metalloid atom</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>calcium atom</t>
+          <t>berkelium atom</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -800,13 +892,17 @@
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>copper atom</t>
+          <t>plutonium atom</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -815,99 +911,123 @@
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ethylene group</t>
+          <t>germanium atom</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>group [chebi]</t>
+          <t>metalloid atom</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>technetium atom</t>
+          <t>device role</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>role</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Rolle, die ein Geräte inne haben kann.</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>phosphorus atom</t>
+          <t>erbium</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nonmetal atom</t>
+          <t>lanthanoid atom</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>xenon atom</t>
+          <t>organosulfur heterocyclic compound</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>molecular entity</t>
+          <t>organosulfur compound</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>krypton atom</t>
+          <t>lithium atom</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>molecular entity</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>device role</t>
+          <t>terbium atom</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>lanthanoid atom</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Rolle, die ein Geräte inne haben kann.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -915,22 +1035,26 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>monocyclic heteroarene</t>
+          <t>chlorine atom</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>heteroarene</t>
+          <t>nonmetal atom</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>hassium atom</t>
+          <t>manganese atom</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -939,148 +1063,188 @@
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>arsenic atom</t>
+          <t>osmium atom</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>metalloid atom</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>oxygen atom</t>
+          <t>rhenium atom</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>chalcogen</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>tungsten</t>
+          <t>samarium atom</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>lanthanoid atom</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>mass percentage based unit</t>
+          <t>silicon atom</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>nonmetal atom</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bohrium atom</t>
+          <t>mass volume percentage based unit</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>scandium atom</t>
+          <t>arsenic atom</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>metalloid atom</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>completely executed planned process</t>
+          <t>radon atom</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>planned process</t>
+          <t>molecular entity</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>organic ion</t>
+          <t>holmium atom</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>organic molecular entity</t>
+          <t>lanthanoid atom</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>sulfur molecular entity</t>
+          <t>ytterbium</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>chalcogen molecular entity</t>
+          <t>lanthanoid atom</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>mendelevium atom</t>
+          <t>dubnium atom</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1089,163 +1253,207 @@
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>yttrium atom</t>
+          <t>antimony atom</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>metalloid atom</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>argon atom</t>
+          <t>lutetium atom</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>molecular entity</t>
+          <t>lanthanoid atom</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>samarium atom</t>
+          <t>molybdenum atom</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>lanthanoid atom</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>terbium atom</t>
+          <t>aluminium oxide</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>lanthanoid atom</t>
+          <t>molecular entity</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>erbium</t>
+          <t>selenium atom</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>lanthanoid atom</t>
+          <t>chalcogen</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>astatine atom</t>
+          <t>oxygen atom</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nonmetal atom</t>
+          <t>chalcogen</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>caesium atom</t>
+          <t>monocyclic heteroarene</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>heteroarene</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Homo sapiens</t>
+          <t>dysprosium atom</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>material entity</t>
+          <t>lanthanoid atom</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>thulium atom</t>
+          <t>cadmium atom</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>lanthanoid atom</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>mole fraction based unit</t>
+          <t>krypton atom</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>molecular entity</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ytterbium</t>
+          <t>praseodymium atom</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1254,28 +1462,36 @@
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>manganese atom</t>
+          <t>boron atom</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>nonmetal atom</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>strontium atom</t>
+          <t>nobelium</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1284,58 +1500,74 @@
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>lead atom</t>
+          <t>pseudohalide anion</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>polyatomic monoanion</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>holmium atom</t>
+          <t>aluminium atom</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>lanthanoid atom</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>lanthanum atom</t>
+          <t>rutherfordium atom</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>lanthanoid atom</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>hafnium atom</t>
+          <t>vanadium atom</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1344,174 +1576,222 @@
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>actinium atom</t>
+          <t>organic ion</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>ion</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1,3-thiazoles</t>
+          <t>curium atom</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>thiazoles [chebi]</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>sodium hydroxide</t>
+          <t>lead atom</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>molecular entity</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>dubnium atom</t>
+          <t>sodium hydroxide</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>molecular entity</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>lanthanoid atom</t>
-        </is>
-      </c>
+      <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr"/>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>organic aromatic compound</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>aromatic compound</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>radium atom</t>
+          <t>phosphorus atom</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>nonmetal atom</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>antimony atom</t>
+          <t>nitrogen molecular entity</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>metalloid atom</t>
+          <t>pnictogen molecular entity</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>molybdenum atom</t>
+          <t>failed planned process</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>planned process</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>osmium atom</t>
+          <t>sulfur atom</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>nonmetal atom</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>chlorine atom</t>
+          <t>einsteinium atom</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>nonmetal atom</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>vanadium atom</t>
+          <t>ruthenium atom</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1520,88 +1800,112 @@
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>fermium</t>
+          <t>promethium atom</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>lanthanoid atom</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>monoanion</t>
+          <t>copper atom</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>anion</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>bromine atom</t>
+          <t>tantalum atom</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>nonmetal atom</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>deprecated class</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr"/>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Lars M Vogt</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
+          <t>strontium atom</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>metal atom</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>helium atom</t>
+          <t>francium atom</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>nonmetal atom</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>neptunium atom</t>
+          <t>hafnium atom</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1610,13 +1914,17 @@
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>bismuth atom</t>
+          <t>rubidium atom</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -1625,13 +1933,17 @@
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>sodium atom</t>
+          <t>mercury atom</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -1640,28 +1952,36 @@
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>cerium</t>
+          <t>uranium atom</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>lanthanoid atom</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>plutonium atom</t>
+          <t>protactinium atom</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -1670,88 +1990,112 @@
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>mass volume percentage based unit</t>
+          <t>hassium atom</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>cadmium atom</t>
+          <t>completely executed planned process</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>planned process</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>gadolinium atom</t>
+          <t>sodium atom</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>lanthanoid atom</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>dysprosium atom</t>
+          <t>tellurium atom</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>lanthanoid atom</t>
+          <t>metalloid atom</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>europium atom</t>
+          <t>1,3-thiazoles</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>lanthanoid atom</t>
+          <t>thiazoles [chebi]</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>titanium atom</t>
+          <t>yttrium atom</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -1760,73 +2104,93 @@
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>barium atom</t>
+          <t>polyatomic monoanion</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>monoanion</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>mercury atom</t>
+          <t>mass percentage based unit</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>elemental carbon</t>
+          <t>tungsten</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>organic molecular entity</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>radon atom</t>
+          <t>argon atom</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>nonmetal atom</t>
+          <t>molecular entity</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>tantalum atom</t>
+          <t>titanium atom</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -1835,13 +2199,17 @@
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>meitnerium atom</t>
+          <t>americium atom</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -1850,58 +2218,74 @@
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>promethium atom</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>lanthanoid atom</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr"/>
+          <t>deprecated class</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Lars M Vogt</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>uranium atom</t>
+          <t>ethylene group</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>group [chebi]</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>boron atom</t>
+          <t>mole fraction based unit</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>nonmetal atom</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>silicon atom</t>
+          <t>fluorine atom</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -1910,28 +2294,36 @@
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>germanium atom</t>
+          <t>neptunium atom</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>metalloid atom</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>aluminium atom</t>
+          <t>zirconium atom</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -1940,13 +2332,17 @@
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>magnesium atom</t>
+          <t>seaborgium atom</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -1955,43 +2351,55 @@
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>carbon nanostructure</t>
+          <t>potassium atom</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>elemental carbon</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>rutherfordium atom</t>
+          <t>neon atom</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>nonmetal atom</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>silver atom</t>
+          <t>technetium atom</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2000,13 +2408,17 @@
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>nobelium</t>
+          <t>meitnerium atom</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2015,13 +2427,17 @@
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>iridium atom</t>
+          <t>darmstadtium</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2030,144 +2446,184 @@
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>lawrencium atom</t>
+          <t>nitrogen atom</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>nonmetal atom</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>potassium atom</t>
+          <t>gadolinium atom</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>lanthanoid atom</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>pseudohalide anion</t>
+          <t>xenon atom</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>polyatomic monoanion</t>
+          <t>molecular entity</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
+          <t>astatine atom</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
           <t>nonmetal atom</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>atom</t>
-        </is>
-      </c>
       <c r="C111" t="inlineStr"/>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>sulfur atom</t>
-        </is>
-      </c>
+      <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>nonmetal atom</t>
+          <t>deprecated class</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>tetraphosphorus decaoxide</t>
+          <t>bismuth atom</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>molecular entity</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>einsteinium atom</t>
+          <t>cerium</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>lanthanoid atom</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr"/>
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>carbon nanostructure</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>deprecated class</t>
+          <t>elemental carbon</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>neon atom</t>
+          <t>carbon group molecular entity</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>nonmetal atom</t>
+          <t>p-block molecular entity</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ruthenium atom</t>
+          <t>niobium atom</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -2176,28 +2632,36 @@
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>hydrogen atom</t>
+          <t>mendelevium atom</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>nonmetal atom</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>zirconium atom</t>
+          <t>silver atom</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2206,43 +2670,55 @@
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>neodymium atom</t>
+          <t>monoanion</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>lanthanoid atom</t>
+          <t>anion</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>polyatomic monoanion</t>
+          <t>carbon atom</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>monoanion</t>
+          <t>nonmetal atom</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>francium atom</t>
+          <t>iridium atom</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -2251,28 +2727,36 @@
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
-      <c r="D122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>selenium atom</t>
+          <t>californium atom</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>chalcogen</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>berkelium atom</t>
+          <t>radium atom</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -2281,28 +2765,36 @@
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>failed planned process</t>
+          <t>elemental carbon</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>planned process</t>
+          <t>elemental molecular entity</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>seaborgium atom</t>
+          <t>fermium</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -2311,28 +2803,36 @@
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>organic aromatic compound</t>
+          <t>tin atom</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>organic cyclic compound</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>protactinium atom</t>
+          <t>thorium</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -2341,7 +2841,11 @@
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr"/>
     </row>
   </sheetData>
